--- a/docs/StructureDefinition-antiemetic-medication.xlsx
+++ b/docs/StructureDefinition-antiemetic-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-antiemetic-medication.xlsx
+++ b/docs/StructureDefinition-antiemetic-medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1077" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="248">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/antiemetic-medication</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/antiemetic-medication</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -509,7 +512,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/antiemetic-medication-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/antiemetic-medication-vs</t>
   </si>
   <si>
     <t>coding.code = //element(*,MedicationType)/DrugCoded/ProductCode@@ -1055,54 +1058,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1140,7 +1145,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="46.30078125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.71875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.70703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
@@ -1158,132 +1163,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1291,10 +1296,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1306,13 +1311,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1363,25 +1368,25 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>20</v>
@@ -1392,10 +1397,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1403,10 +1408,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1415,19 +1420,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1477,13 +1482,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1506,10 +1511,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1517,10 +1522,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1529,16 +1534,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1589,19 +1594,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1618,10 +1623,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1629,31 +1634,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1703,19 +1708,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1732,10 +1737,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1743,10 +1748,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1758,16 +1763,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1793,13 +1798,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -1817,19 +1822,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -1846,21 +1851,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1872,16 +1877,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1931,25 +1936,25 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>20</v>
@@ -1960,21 +1965,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1986,16 +1991,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2045,13 +2050,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2063,7 +2068,7 @@
         <v>20</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>20</v>
@@ -2074,21 +2079,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2100,16 +2105,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2159,25 +2164,25 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>20</v>
@@ -2188,45 +2193,45 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
@@ -2275,25 +2280,25 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>20</v>
@@ -2304,10 +2309,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2315,10 +2320,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2327,19 +2332,19 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2389,28 +2394,28 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>20</v>
@@ -2418,10 +2423,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2429,31 +2434,31 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2479,11 +2484,11 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -2501,39 +2506,39 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2541,31 +2546,31 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2591,13 +2596,13 @@
         <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>20</v>
@@ -2615,25 +2620,25 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>20</v>
@@ -2644,10 +2649,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2655,10 +2660,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2667,16 +2672,16 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2727,39 +2732,39 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2767,13 +2772,13 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>20</v>
@@ -2782,16 +2787,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2817,13 +2822,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -2841,39 +2846,39 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2881,10 +2886,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -2893,16 +2898,16 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2953,25 +2958,25 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>20</v>
@@ -2982,10 +2987,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2993,10 +2998,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3008,16 +3013,16 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3067,25 +3072,25 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>20</v>
@@ -3096,10 +3101,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3107,10 +3112,10 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
@@ -3122,13 +3127,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3179,13 +3184,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -3197,7 +3202,7 @@
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>20</v>
@@ -3208,21 +3213,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3234,16 +3239,16 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3293,25 +3298,25 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -3322,45 +3327,45 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3409,25 +3414,25 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
@@ -3438,10 +3443,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3449,10 +3454,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3464,17 +3469,17 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3523,39 +3528,39 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3563,10 +3568,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -3578,17 +3583,17 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -3637,25 +3642,25 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
@@ -3666,10 +3671,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3677,10 +3682,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>20</v>
@@ -3692,13 +3697,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3749,39 +3754,39 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3789,10 +3794,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -3804,13 +3809,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3861,25 +3866,25 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
@@ -3890,10 +3895,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3901,10 +3906,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>20</v>
@@ -3916,13 +3921,13 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3973,13 +3978,13 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
@@ -3991,7 +3996,7 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
@@ -4002,21 +4007,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4028,16 +4033,16 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4087,25 +4092,25 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4116,45 +4121,45 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -4203,25 +4208,25 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -4232,10 +4237,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4243,10 +4248,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4258,13 +4263,13 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4315,39 +4320,39 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4355,10 +4360,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -4370,13 +4375,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4427,31 +4432,31 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
